--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Johan Råghall, Marie Persson, Torun Ingrid Maria Jacobsson, Lina Hällström, Cajsa Björkén, Klas Magnusson, Isak Falk Eliasson, Mattias Dalkvist</t>
+          <t>Johan Råghall, Mattias Dalkvist, Isak Falk Eliasson, Klas Magnusson, Cajsa Björkén, Lina Hällström, Torun Ingrid Maria Jacobsson, Marie Persson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
@@ -28565,7 +28565,7 @@
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Johan Råghall, Marie Persson, Torun Ingrid Maria Jacobsson, Lina Hällström, Cajsa Björkén, Klas Magnusson, Isak Falk Eliasson, Mattias Dalkvist</t>
+          <t>Johan Råghall, Mattias Dalkvist, Isak Falk Eliasson, Klas Magnusson, Cajsa Björkén, Lina Hällström, Torun Ingrid Maria Jacobsson, Marie Persson</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
@@ -34639,7 +34639,7 @@
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Lina Hällström, Klas Magnusson, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Klas Magnusson, Lina Hällström, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Johan Råghall, Mattias Dalkvist, Isak Falk Eliasson, Klas Magnusson, Cajsa Björkén, Lina Hällström, Torun Ingrid Maria Jacobsson, Marie Persson</t>
+          <t>Johan Råghall, Marie Persson, Torun Ingrid Maria Jacobsson, Lina Hällström, Cajsa Björkén, Klas Magnusson, Isak Falk Eliasson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
@@ -28565,7 +28565,7 @@
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Johan Råghall, Mattias Dalkvist, Isak Falk Eliasson, Klas Magnusson, Cajsa Björkén, Lina Hällström, Torun Ingrid Maria Jacobsson, Marie Persson</t>
+          <t>Johan Råghall, Marie Persson, Torun Ingrid Maria Jacobsson, Lina Hällström, Cajsa Björkén, Klas Magnusson, Isak Falk Eliasson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
@@ -34639,7 +34639,7 @@
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Klas Magnusson, Lina Hällström, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Lina Hällström, Klas Magnusson, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -26664,7 +26664,7 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -27851,7 +27851,7 @@
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -28201,7 +28201,7 @@
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -29738,7 +29738,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
@@ -29849,7 +29849,7 @@
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -30090,7 +30090,7 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
@@ -32178,7 +32178,7 @@
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY317"/>
+  <dimension ref="A1:AZ317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305579</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293798</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331635</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1203,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1259,6 +1284,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298649</t>
         </is>
       </c>
     </row>
@@ -1372,6 +1402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293778</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293782</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293799</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1705,6 +1750,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293809</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1816,6 +1866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293813</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293830</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2038,6 +2098,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293834</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2149,6 +2214,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293850</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,6 +2330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331604</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2371,6 +2446,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331613</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2482,6 +2562,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331616</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2613,6 +2698,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305590</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2722,6 +2812,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293807</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2856,7 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2837,6 +2932,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298644</t>
         </is>
       </c>
     </row>
@@ -2950,6 +3050,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3081,6 +3186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305592</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3192,6 +3302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293864</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3303,6 +3418,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293779</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3414,6 +3534,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293781</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3525,6 +3650,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298017</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3659,6 +3789,11 @@
       <c r="AY27" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300044</t>
         </is>
       </c>
     </row>
@@ -3776,6 +3911,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135510816</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3892,6 +4032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293869</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4003,6 +4148,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331647</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4132,6 +4282,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305591</t>
         </is>
       </c>
     </row>
@@ -4258,6 +4413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293775</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4369,6 +4529,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331645</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4480,6 +4645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293801</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4591,6 +4761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293816</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4702,6 +4877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293824</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4813,6 +4993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293849</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4924,6 +5109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331638</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5035,6 +5225,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293784</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5146,6 +5341,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293785</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5257,6 +5457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293792</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5368,6 +5573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293794</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5479,6 +5689,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293800</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5590,6 +5805,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293803</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5701,6 +5921,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293808</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5812,6 +6037,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293814</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5923,6 +6153,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293822</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6034,6 +6269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293831</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6145,6 +6385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293843</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6256,6 +6501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293866</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6367,6 +6617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293867</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6478,6 +6733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293868</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6589,6 +6849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293870</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6700,6 +6965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293885</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6811,6 +7081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293888</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6922,6 +7197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293892</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7033,6 +7313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293894</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7144,6 +7429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293895</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7255,6 +7545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293896</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7366,6 +7661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293898</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7477,6 +7777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293899</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7588,6 +7893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293901</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7699,6 +8009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293903</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7810,6 +8125,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293908</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7921,6 +8241,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293918</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8032,6 +8357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297982</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8158,6 +8488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297987</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8269,6 +8604,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297995</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8380,6 +8720,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298003</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8491,6 +8836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298005</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8602,6 +8952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298008</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8713,6 +9068,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298016</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8824,6 +9184,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298018</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8935,6 +9300,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298022</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8969,7 +9339,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -9044,6 +9414,11 @@
       <c r="AY75" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298624</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9458,7 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -9159,6 +9534,11 @@
       <c r="AY76" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298625</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9575,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
@@ -9270,6 +9650,11 @@
       <c r="AY77" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298634</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9694,7 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -9385,6 +9770,11 @@
       <c r="AY78" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298640</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9814,7 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -9500,6 +9890,11 @@
       <c r="AY79" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298641</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9934,7 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -9615,6 +10010,11 @@
       <c r="AY80" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298643</t>
         </is>
       </c>
     </row>
@@ -9654,7 +10054,7 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -9730,6 +10130,11 @@
       <c r="AY81" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298650</t>
         </is>
       </c>
     </row>
@@ -9853,6 +10258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300029</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9974,6 +10384,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300030</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10100,6 +10515,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300034</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10226,6 +10646,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300045</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10337,6 +10762,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305574</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10448,6 +10878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331589</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10559,6 +10994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331597</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10670,6 +11110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331606</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10781,6 +11226,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331611</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10892,6 +11342,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331612</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11003,6 +11458,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331615</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11114,6 +11574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331625</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11225,6 +11690,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331626</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11341,6 +11811,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331627</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11452,6 +11927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331629</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11563,6 +12043,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331642</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11674,6 +12159,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293776</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11785,6 +12275,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293783</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11896,6 +12391,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293791</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12007,6 +12507,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293795</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12118,6 +12623,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293810</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12229,6 +12739,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293820</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12340,6 +12855,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293846</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12451,6 +12971,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293851</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12562,6 +13087,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293854</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12673,6 +13203,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293857</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12784,6 +13319,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293878</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12895,6 +13435,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293881</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13006,6 +13551,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297981</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13117,6 +13667,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297992</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13228,6 +13783,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298001</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13339,6 +13899,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298012</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13460,6 +14025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300025</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13596,6 +14166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300027</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13732,6 +14307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300032</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13863,6 +14443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300040</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13994,6 +14579,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305585</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14105,6 +14695,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331603</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14216,6 +14811,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331637</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14327,6 +14927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293889</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14438,6 +15043,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298009</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14549,6 +15159,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298019</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14680,6 +15295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300046</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14811,6 +15431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305578</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14922,6 +15547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331610</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15058,6 +15688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300042</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15169,6 +15804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331621</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15280,6 +15920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293774</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15391,6 +16036,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293780</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15502,6 +16152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293787</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15613,6 +16268,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293806</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15724,6 +16384,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293811</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15835,6 +16500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293812</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15946,6 +16616,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293817</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16057,6 +16732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293829</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16168,6 +16848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293833</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16279,6 +16964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293855</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16390,6 +17080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293858</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16501,6 +17196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293875</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16612,6 +17312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293877</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16721,6 +17426,11 @@
       <c r="AY142" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297990</t>
         </is>
       </c>
     </row>
@@ -16760,7 +17470,7 @@
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
@@ -16836,6 +17546,11 @@
       <c r="AY143" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298631</t>
         </is>
       </c>
     </row>
@@ -16974,6 +17689,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300041</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17105,6 +17825,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305570</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17216,6 +17941,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331591</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17327,6 +18057,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331592</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17438,6 +18173,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331595</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17549,6 +18289,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331598</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17660,6 +18405,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331599</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17771,6 +18521,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331608</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17882,6 +18637,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331622</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17993,6 +18753,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331632</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18102,6 +18867,11 @@
       <c r="AY154" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331633</t>
         </is>
       </c>
     </row>
@@ -18219,6 +18989,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512789</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18256,7 +19031,7 @@
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
@@ -18332,6 +19107,11 @@
       <c r="AY156" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298623</t>
         </is>
       </c>
     </row>
@@ -18449,6 +19229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511061</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18560,6 +19345,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293805</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18676,6 +19466,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293871</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18807,6 +19602,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293886</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18923,6 +19723,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293882</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19049,6 +19854,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297978</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19173,6 +19983,11 @@
       <c r="AY163" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297993</t>
         </is>
       </c>
     </row>
@@ -19212,7 +20027,7 @@
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
@@ -19288,6 +20103,11 @@
       <c r="AY164" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298648</t>
         </is>
       </c>
     </row>
@@ -19401,6 +20221,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293848</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19527,6 +20352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293872</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19638,6 +20468,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293786</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19749,6 +20584,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293790</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19860,6 +20700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293796</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19971,6 +20816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293818</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20082,6 +20932,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293823</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20193,6 +21048,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293842</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20304,6 +21164,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297991</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20415,6 +21280,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297999</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20526,6 +21396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298000</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20647,6 +21522,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300026</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20783,6 +21663,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300028</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20919,6 +21804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300033</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21050,6 +21940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305583</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21161,6 +22056,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331601</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21272,6 +22172,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331636</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21408,6 +22313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293876</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21544,6 +22454,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293883</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21665,6 +22580,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293890</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21801,6 +22721,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293891</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21920,6 +22845,11 @@
       <c r="AY186" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293893</t>
         </is>
       </c>
     </row>
@@ -22042,6 +22972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293897</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22158,6 +23093,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293900</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22279,6 +23219,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293902</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22400,6 +23345,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293904</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22521,6 +23471,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293905</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22642,6 +23597,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293907</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22763,6 +23723,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293910</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22884,6 +23849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293911</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23005,6 +23975,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293912</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23126,6 +24101,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293915</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -23247,6 +24227,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293919</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23368,6 +24353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293920</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23489,6 +24479,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293921</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23610,6 +24605,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293922</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23731,6 +24731,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293923</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23852,6 +24857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293924</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23973,6 +24983,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293926</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24094,6 +25109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293929</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -24215,6 +25235,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293930</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24336,6 +25361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293931</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24457,6 +25487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293932</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24578,6 +25613,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293933</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24699,6 +25739,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293934</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24820,6 +25865,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293935</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24941,6 +25991,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297983</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25062,6 +26117,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297986</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25183,6 +26243,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297988</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25304,6 +26369,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297994</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -25425,6 +26495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297996</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -25546,6 +26621,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297997</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25667,6 +26747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298002</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25788,6 +26873,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298007</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25909,6 +26999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298010</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26030,6 +27125,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298011</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26151,6 +27251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298013</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26276,6 +27381,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298021</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -26397,6 +27507,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298023</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26439,7 +27554,7 @@
       <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
@@ -26519,6 +27634,11 @@
       <c r="AY224" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298656</t>
         </is>
       </c>
     </row>
@@ -26645,6 +27765,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299555</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26776,6 +27901,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300048</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26895,6 +28025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511047</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -27014,6 +28149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512979</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -27138,6 +28278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513031</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -27257,6 +28402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513062</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -27373,6 +28523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293788</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -27489,6 +28644,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293826</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -27617,6 +28777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305567</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -27733,6 +28898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305572</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -27849,6 +29019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305582</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27965,6 +29140,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331624</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -28081,6 +29261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331634</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -28197,6 +29382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331641</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -28333,6 +29523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305571</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -28449,6 +29644,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293873</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -28570,6 +29770,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293887</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -28688,6 +29893,11 @@
       <c r="AY242" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293916</t>
         </is>
       </c>
     </row>
@@ -28728,7 +29938,7 @@
       <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q243" t="n">
@@ -28803,6 +30013,11 @@
       <c r="AY243" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298637</t>
         </is>
       </c>
     </row>
@@ -28920,6 +30135,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305581</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -29040,6 +30260,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293772</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -29074,7 +30299,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q246" t="n">
@@ -29149,6 +30374,11 @@
       <c r="AY246" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298651</t>
         </is>
       </c>
     </row>
@@ -29265,7 +30495,16 @@
           <t>Klas Magnusson, Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
-      <c r="AY247" t="inlineStr"/>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135307481</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -29402,6 +30641,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305600</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -29516,6 +30760,11 @@
       <c r="AY249" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305596</t>
         </is>
       </c>
     </row>
@@ -29556,7 +30805,7 @@
       <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q250" t="n">
@@ -29632,6 +30881,11 @@
       <c r="AY250" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298647</t>
         </is>
       </c>
     </row>
@@ -29672,7 +30926,7 @@
       <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
@@ -29753,6 +31007,11 @@
       <c r="AY251" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298652</t>
         </is>
       </c>
     </row>
@@ -29793,7 +31052,7 @@
       <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q252" t="n">
@@ -29869,6 +31128,11 @@
       <c r="AY252" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298658</t>
         </is>
       </c>
     </row>
@@ -29909,7 +31173,7 @@
       <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
@@ -29990,6 +31254,11 @@
       <c r="AY253" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298659</t>
         </is>
       </c>
     </row>
@@ -30112,6 +31381,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300049</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -30230,6 +31504,11 @@
       <c r="AY255" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300050</t>
         </is>
       </c>
     </row>
@@ -30270,7 +31549,7 @@
       <c r="N256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
@@ -30346,6 +31625,11 @@
       <c r="AY256" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298626</t>
         </is>
       </c>
     </row>
@@ -30386,7 +31670,7 @@
       <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
@@ -30462,6 +31746,11 @@
       <c r="AY257" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298642</t>
         </is>
       </c>
     </row>
@@ -30502,7 +31791,7 @@
       <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q258" t="n">
@@ -30578,6 +31867,11 @@
       <c r="AY258" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298645</t>
         </is>
       </c>
     </row>
@@ -30618,7 +31912,7 @@
       <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q259" t="n">
@@ -30694,6 +31988,11 @@
       <c r="AY259" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298655</t>
         </is>
       </c>
     </row>
@@ -30807,6 +32106,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305575</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -30918,6 +32222,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305587</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -31048,6 +32357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300024</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -31157,6 +32471,11 @@
       <c r="AY263" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305577</t>
         </is>
       </c>
     </row>
@@ -31275,6 +32594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513209</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -31391,6 +32715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300036</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -31507,6 +32836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300047</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -31633,6 +32967,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297980</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -31744,6 +33083,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297985</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -31855,6 +33199,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297998</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -31966,6 +33315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298006</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -32077,6 +33431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293821</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -32188,6 +33547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293852</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -32299,6 +33663,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293874</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -32410,6 +33779,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293880</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -32521,6 +33895,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293917</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -32632,6 +34011,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297989</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -32743,6 +34127,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298004</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -32854,6 +34243,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299553</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -32965,6 +34359,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299554</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -33101,6 +34500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300038</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -33232,6 +34636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300043</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -33363,6 +34772,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305584</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -33474,6 +34888,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331620</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -33585,6 +35004,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331623</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -33696,6 +35120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331630</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -33807,6 +35236,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293793</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -33918,6 +35352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293819</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -34029,6 +35468,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293825</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -34140,6 +35584,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293828</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -34251,6 +35700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293832</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -34362,6 +35816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293845</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -34473,6 +35932,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293847</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -34584,6 +36048,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293879</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -34710,6 +36179,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300039</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -34821,6 +36295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331588</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -34932,6 +36411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331593</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -35043,6 +36527,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331594</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -35154,6 +36643,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331617</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -35265,6 +36759,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331628</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -35376,6 +36875,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293777</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -35487,6 +36991,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293856</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -35521,7 +37030,7 @@
       <c r="I302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q302" t="n">
@@ -35596,6 +37105,11 @@
       <c r="AY302" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298629</t>
         </is>
       </c>
     </row>
@@ -35632,7 +37146,7 @@
       <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q303" t="n">
@@ -35707,6 +37221,11 @@
       <c r="AY303" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298633</t>
         </is>
       </c>
     </row>
@@ -35746,7 +37265,7 @@
       <c r="N304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q304" t="n">
@@ -35822,6 +37341,11 @@
       <c r="AY304" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298639</t>
         </is>
       </c>
     </row>
@@ -35861,7 +37385,7 @@
       <c r="N305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Tis Gr 3_Saravallen_topo, Pi lm</t>
+          <t>Saravallen, Pi lm</t>
         </is>
       </c>
       <c r="Q305" t="n">
@@ -35937,6 +37461,11 @@
       <c r="AY305" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298657</t>
         </is>
       </c>
     </row>
@@ -36055,6 +37584,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331590</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -36166,6 +37700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331596</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -36277,6 +37816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331605</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -36388,6 +37932,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331607</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -36499,6 +38048,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331609</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -36610,6 +38164,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331618</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -36721,6 +38280,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331640</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -36832,6 +38396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331644</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -36941,6 +38510,11 @@
       <c r="AY314" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331646</t>
         </is>
       </c>
     </row>
@@ -37058,6 +38632,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293815</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -37173,6 +38752,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293827</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -37284,8 +38868,331 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135305595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
@@ -35344,7 +35344,7 @@
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -35460,7 +35460,7 @@
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -38624,7 +38624,7 @@
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -38744,7 +38744,7 @@
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135305579</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>135331631</v>
       </c>
       <c r="B3" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>135293798</v>
       </c>
       <c r="B4" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135331635</v>
       </c>
       <c r="B5" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135298649</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135293778</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1413,7 +1413,7 @@
         <v>135293782</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1529,7 +1529,7 @@
         <v>135293799</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>135293809</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135293813</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1877,7 +1877,7 @@
         <v>135293830</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1993,7 +1993,7 @@
         <v>135293834</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2109,7 +2109,7 @@
         <v>135293850</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135331604</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135331613</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135331616</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135305590</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135293807</v>
       </c>
       <c r="B19" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>135298644</v>
       </c>
       <c r="B20" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135298020</v>
       </c>
       <c r="B21" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>135305592</v>
       </c>
       <c r="B22" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>135293864</v>
       </c>
       <c r="B23" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>135293779</v>
       </c>
       <c r="B24" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135293781</v>
       </c>
       <c r="B25" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3545,7 +3545,7 @@
         <v>135298017</v>
       </c>
       <c r="B26" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135300044</v>
       </c>
       <c r="B27" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135510816</v>
       </c>
       <c r="B28" t="n">
-        <v>90724</v>
+        <v>90766</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135293869</v>
       </c>
       <c r="B29" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135331647</v>
       </c>
       <c r="B30" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>135305591</v>
       </c>
       <c r="B31" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>135293775</v>
       </c>
       <c r="B32" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135331645</v>
       </c>
       <c r="B33" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135293801</v>
       </c>
       <c r="B34" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4656,7 +4656,7 @@
         <v>135293816</v>
       </c>
       <c r="B35" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>135293824</v>
       </c>
       <c r="B36" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4888,7 +4888,7 @@
         <v>135293849</v>
       </c>
       <c r="B37" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>135331638</v>
       </c>
       <c r="B38" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>135293784</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>135293785</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135293792</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5468,7 +5468,7 @@
         <v>135293794</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>135293800</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5700,7 +5700,7 @@
         <v>135293803</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>135293808</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135293814</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135293822</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>135293831</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6280,7 +6280,7 @@
         <v>135293843</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6396,7 +6396,7 @@
         <v>135293866</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135293867</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>135293868</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135293870</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>135293885</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>135293888</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>135293892</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>135293894</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>135293895</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>135293896</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>135293898</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>135293899</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>135293901</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>135293903</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>135293908</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>135293918</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>135297982</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>135297987</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>135297995</v>
       </c>
       <c r="B68" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>135298003</v>
       </c>
       <c r="B69" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>135298005</v>
       </c>
       <c r="B70" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>135298008</v>
       </c>
       <c r="B71" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>135298016</v>
       </c>
       <c r="B72" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>135298018</v>
       </c>
       <c r="B73" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>135298022</v>
       </c>
       <c r="B74" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>135298624</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>135298625</v>
       </c>
       <c r="B76" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>135298634</v>
       </c>
       <c r="B77" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>135298640</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>135298641</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>135298643</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>135298650</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>135300029</v>
       </c>
       <c r="B82" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>135300030</v>
       </c>
       <c r="B83" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>135300034</v>
       </c>
       <c r="B84" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>135300045</v>
       </c>
       <c r="B85" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>135305574</v>
       </c>
       <c r="B86" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>135331589</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>135331597</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>135331606</v>
       </c>
       <c r="B89" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>135331611</v>
       </c>
       <c r="B90" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>135331612</v>
       </c>
       <c r="B91" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135331615</v>
       </c>
       <c r="B92" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>135331625</v>
       </c>
       <c r="B93" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>135331626</v>
       </c>
       <c r="B94" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>135331627</v>
       </c>
       <c r="B95" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>135331629</v>
       </c>
       <c r="B96" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>135331642</v>
       </c>
       <c r="B97" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>135293776</v>
       </c>
       <c r="B98" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>135293783</v>
       </c>
       <c r="B99" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>135293791</v>
       </c>
       <c r="B100" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12402,7 +12402,7 @@
         <v>135293795</v>
       </c>
       <c r="B101" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>135293810</v>
       </c>
       <c r="B102" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>135293820</v>
       </c>
       <c r="B103" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12750,7 +12750,7 @@
         <v>135293846</v>
       </c>
       <c r="B104" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>135293851</v>
       </c>
       <c r="B105" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>135293854</v>
       </c>
       <c r="B106" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13098,7 +13098,7 @@
         <v>135293857</v>
       </c>
       <c r="B107" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>135293878</v>
       </c>
       <c r="B108" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135293881</v>
       </c>
       <c r="B109" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>135297981</v>
       </c>
       <c r="B110" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>135297992</v>
       </c>
       <c r="B111" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>135298001</v>
       </c>
       <c r="B112" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135298012</v>
       </c>
       <c r="B113" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>135300025</v>
       </c>
       <c r="B114" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>135300027</v>
       </c>
       <c r="B115" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>135300032</v>
       </c>
       <c r="B116" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>135300040</v>
       </c>
       <c r="B117" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>135305585</v>
       </c>
       <c r="B118" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>135331603</v>
       </c>
       <c r="B119" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>135331637</v>
       </c>
       <c r="B120" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>135293889</v>
       </c>
       <c r="B121" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>135298009</v>
       </c>
       <c r="B122" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>135298019</v>
       </c>
       <c r="B123" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>135300046</v>
       </c>
       <c r="B124" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>135305578</v>
       </c>
       <c r="B125" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135331610</v>
       </c>
       <c r="B126" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>135300042</v>
       </c>
       <c r="B127" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>135331621</v>
       </c>
       <c r="B128" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>135293774</v>
       </c>
       <c r="B129" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>135293780</v>
       </c>
       <c r="B130" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>135293787</v>
       </c>
       <c r="B131" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>135293806</v>
       </c>
       <c r="B132" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>135293811</v>
       </c>
       <c r="B133" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>135293812</v>
       </c>
       <c r="B134" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16511,7 +16511,7 @@
         <v>135293817</v>
       </c>
       <c r="B135" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>135293829</v>
       </c>
       <c r="B136" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>135293833</v>
       </c>
       <c r="B137" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -16859,7 +16859,7 @@
         <v>135293855</v>
       </c>
       <c r="B138" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>135293858</v>
       </c>
       <c r="B139" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>135293875</v>
       </c>
       <c r="B140" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>135293877</v>
       </c>
       <c r="B141" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>135297990</v>
       </c>
       <c r="B142" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>135298631</v>
       </c>
       <c r="B143" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>135300041</v>
       </c>
       <c r="B144" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>135305570</v>
       </c>
       <c r="B145" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>135331591</v>
       </c>
       <c r="B146" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135331592</v>
       </c>
       <c r="B147" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>135331595</v>
       </c>
       <c r="B148" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>135331598</v>
       </c>
       <c r="B149" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>135331599</v>
       </c>
       <c r="B150" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>135331608</v>
       </c>
       <c r="B151" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>135331622</v>
       </c>
       <c r="B152" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>135331632</v>
       </c>
       <c r="B153" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>135331633</v>
       </c>
       <c r="B154" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>135512789</v>
       </c>
       <c r="B155" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>135298623</v>
       </c>
       <c r="B156" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>135511061</v>
       </c>
       <c r="B157" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>135293805</v>
       </c>
       <c r="B158" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>135293871</v>
       </c>
       <c r="B159" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>135293886</v>
       </c>
       <c r="B160" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>135293882</v>
       </c>
       <c r="B161" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>135297978</v>
       </c>
       <c r="B162" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>135297993</v>
       </c>
       <c r="B163" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135298648</v>
       </c>
       <c r="B164" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>135293848</v>
       </c>
       <c r="B165" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>135293872</v>
       </c>
       <c r="B166" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>135293786</v>
       </c>
       <c r="B167" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>135293790</v>
       </c>
       <c r="B168" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>135293796</v>
       </c>
       <c r="B169" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>135293818</v>
       </c>
       <c r="B170" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>135293823</v>
       </c>
       <c r="B171" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -20943,7 +20943,7 @@
         <v>135293842</v>
       </c>
       <c r="B172" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>135297991</v>
       </c>
       <c r="B173" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>135297999</v>
       </c>
       <c r="B174" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>135298000</v>
       </c>
       <c r="B175" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>135300026</v>
       </c>
       <c r="B176" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>135300028</v>
       </c>
       <c r="B177" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>135300033</v>
       </c>
       <c r="B178" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>135305583</v>
       </c>
       <c r="B179" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>135331601</v>
       </c>
       <c r="B180" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>135331636</v>
       </c>
       <c r="B181" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>135293876</v>
       </c>
       <c r="B182" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>135293883</v>
       </c>
       <c r="B183" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>135293890</v>
       </c>
       <c r="B184" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>135293891</v>
       </c>
       <c r="B185" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>135293893</v>
       </c>
       <c r="B186" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>135293897</v>
       </c>
       <c r="B187" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>135293900</v>
       </c>
       <c r="B188" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>135293902</v>
       </c>
       <c r="B189" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>135293904</v>
       </c>
       <c r="B190" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>135293905</v>
       </c>
       <c r="B191" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>135293907</v>
       </c>
       <c r="B192" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>135293910</v>
       </c>
       <c r="B193" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>135293911</v>
       </c>
       <c r="B194" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>135293912</v>
       </c>
       <c r="B195" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>135293915</v>
       </c>
       <c r="B196" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>135293919</v>
       </c>
       <c r="B197" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>135293920</v>
       </c>
       <c r="B198" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>135293921</v>
       </c>
       <c r="B199" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>135293922</v>
       </c>
       <c r="B200" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>135293923</v>
       </c>
       <c r="B201" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>135293924</v>
       </c>
       <c r="B202" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>135293926</v>
       </c>
       <c r="B203" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>135293929</v>
       </c>
       <c r="B204" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>135293930</v>
       </c>
       <c r="B205" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>135293931</v>
       </c>
       <c r="B206" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>135293932</v>
       </c>
       <c r="B207" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>135293933</v>
       </c>
       <c r="B208" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>135293934</v>
       </c>
       <c r="B209" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>135293935</v>
       </c>
       <c r="B210" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>135297983</v>
       </c>
       <c r="B211" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>135297986</v>
       </c>
       <c r="B212" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>135297988</v>
       </c>
       <c r="B213" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>135297994</v>
       </c>
       <c r="B214" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>135297996</v>
       </c>
       <c r="B215" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>135297997</v>
       </c>
       <c r="B216" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>135298002</v>
       </c>
       <c r="B217" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>135298007</v>
       </c>
       <c r="B218" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>135298010</v>
       </c>
       <c r="B219" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>135298011</v>
       </c>
       <c r="B220" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>135298013</v>
       </c>
       <c r="B221" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>135298021</v>
       </c>
       <c r="B222" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>135298023</v>
       </c>
       <c r="B223" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>135298656</v>
       </c>
       <c r="B224" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>135299555</v>
       </c>
       <c r="B225" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>135300048</v>
       </c>
       <c r="B226" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>135511047</v>
       </c>
       <c r="B227" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>135512979</v>
       </c>
       <c r="B228" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>135513031</v>
       </c>
       <c r="B229" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>135513062</v>
       </c>
       <c r="B230" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>135293788</v>
       </c>
       <c r="B231" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>135293826</v>
       </c>
       <c r="B232" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>135305567</v>
       </c>
       <c r="B233" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>135305572</v>
       </c>
       <c r="B234" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>135305582</v>
       </c>
       <c r="B235" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>135331624</v>
       </c>
       <c r="B236" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>135331634</v>
       </c>
       <c r="B237" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>135331641</v>
       </c>
       <c r="B238" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>135293873</v>
       </c>
       <c r="B240" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>135293887</v>
       </c>
       <c r="B241" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>135293916</v>
       </c>
       <c r="B242" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>135298637</v>
       </c>
       <c r="B243" t="n">
-        <v>58138</v>
+        <v>58143</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>135305581</v>
       </c>
       <c r="B244" t="n">
-        <v>58138</v>
+        <v>58143</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>135293772</v>
       </c>
       <c r="B245" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>135298651</v>
       </c>
       <c r="B246" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>135305600</v>
       </c>
       <c r="B248" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>135305596</v>
       </c>
       <c r="B249" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>135298647</v>
       </c>
       <c r="B250" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>135298652</v>
       </c>
       <c r="B251" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>135298658</v>
       </c>
       <c r="B252" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>135298659</v>
       </c>
       <c r="B253" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>135300049</v>
       </c>
       <c r="B254" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>135300050</v>
       </c>
       <c r="B255" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>135298626</v>
       </c>
       <c r="B256" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>135298642</v>
       </c>
       <c r="B257" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>135298645</v>
       </c>
       <c r="B258" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>135298655</v>
       </c>
       <c r="B259" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>135305575</v>
       </c>
       <c r="B260" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>135305587</v>
       </c>
       <c r="B261" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>135300024</v>
       </c>
       <c r="B262" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>135305577</v>
       </c>
       <c r="B263" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>135513209</v>
       </c>
       <c r="B264" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>135300036</v>
       </c>
       <c r="B265" t="n">
-        <v>103907</v>
+        <v>103958</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>135300047</v>
       </c>
       <c r="B266" t="n">
-        <v>103907</v>
+        <v>103958</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>135297980</v>
       </c>
       <c r="B267" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>135297985</v>
       </c>
       <c r="B268" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>135297998</v>
       </c>
       <c r="B269" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>135298006</v>
       </c>
       <c r="B270" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>135293821</v>
       </c>
       <c r="B271" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
@@ -33442,7 +33442,7 @@
         <v>135293852</v>
       </c>
       <c r="B272" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
@@ -33558,7 +33558,7 @@
         <v>135293874</v>
       </c>
       <c r="B273" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>135293880</v>
       </c>
       <c r="B274" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>135293917</v>
       </c>
       <c r="B275" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>135297989</v>
       </c>
       <c r="B276" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>135298004</v>
       </c>
       <c r="B277" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>135299553</v>
       </c>
       <c r="B278" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>135299554</v>
       </c>
       <c r="B279" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>135300038</v>
       </c>
       <c r="B280" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>135300043</v>
       </c>
       <c r="B281" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>135305584</v>
       </c>
       <c r="B282" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>135331620</v>
       </c>
       <c r="B283" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>135331623</v>
       </c>
       <c r="B284" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>135331630</v>
       </c>
       <c r="B285" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>135293793</v>
       </c>
       <c r="B286" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -35247,7 +35247,7 @@
         <v>135293819</v>
       </c>
       <c r="B287" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -35363,7 +35363,7 @@
         <v>135293825</v>
       </c>
       <c r="B288" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -35479,7 +35479,7 @@
         <v>135293828</v>
       </c>
       <c r="B289" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>135293832</v>
       </c>
       <c r="B290" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
@@ -35711,7 +35711,7 @@
         <v>135293845</v>
       </c>
       <c r="B291" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
@@ -35827,7 +35827,7 @@
         <v>135293847</v>
       </c>
       <c r="B292" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>135293879</v>
       </c>
       <c r="B293" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>135300039</v>
       </c>
       <c r="B294" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>135331588</v>
       </c>
       <c r="B295" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>135331593</v>
       </c>
       <c r="B296" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>135331594</v>
       </c>
       <c r="B297" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>135331617</v>
       </c>
       <c r="B298" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>135331628</v>
       </c>
       <c r="B299" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>135293777</v>
       </c>
       <c r="B300" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>135293856</v>
       </c>
       <c r="B301" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
+          <t>Cajsa Björkén, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson, Mattias Dalkvist, Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -37002,7 +37002,7 @@
         <v>135298629</v>
       </c>
       <c r="B302" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>135298633</v>
       </c>
       <c r="B303" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>135298639</v>
       </c>
       <c r="B304" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>135298657</v>
       </c>
       <c r="B305" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>135331590</v>
       </c>
       <c r="B306" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>135331596</v>
       </c>
       <c r="B307" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>135331605</v>
       </c>
       <c r="B308" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>135331607</v>
       </c>
       <c r="B309" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>135331609</v>
       </c>
       <c r="B310" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>135331618</v>
       </c>
       <c r="B311" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>135331640</v>
       </c>
       <c r="B312" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>135331644</v>
       </c>
       <c r="B313" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>135331646</v>
       </c>
       <c r="B314" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>135293815</v>
       </c>
       <c r="B315" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -38643,7 +38643,7 @@
         <v>135293827</v>
       </c>
       <c r="B316" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
@@ -38763,7 +38763,7 @@
         <v>135305595</v>
       </c>
       <c r="B317" t="n">
-        <v>95840</v>
+        <v>95884</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135305579</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>135331631</v>
       </c>
       <c r="B3" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>135293798</v>
       </c>
       <c r="B4" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135331635</v>
       </c>
       <c r="B5" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135298649</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135293778</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135293782</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1529,7 +1529,7 @@
         <v>135293799</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135293809</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135293813</v>
       </c>
       <c r="B11" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1877,7 +1877,7 @@
         <v>135293830</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135293834</v>
       </c>
       <c r="B13" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2109,7 +2109,7 @@
         <v>135293850</v>
       </c>
       <c r="B14" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135331604</v>
       </c>
       <c r="B15" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135331613</v>
       </c>
       <c r="B16" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135331616</v>
       </c>
       <c r="B17" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135305590</v>
       </c>
       <c r="B18" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135293807</v>
       </c>
       <c r="B19" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>135298644</v>
       </c>
       <c r="B20" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135298020</v>
       </c>
       <c r="B21" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>135305592</v>
       </c>
       <c r="B22" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>135293864</v>
       </c>
       <c r="B23" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>135293779</v>
       </c>
       <c r="B24" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135293781</v>
       </c>
       <c r="B25" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Isak Falk Eliasson, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3545,7 +3545,7 @@
         <v>135298017</v>
       </c>
       <c r="B26" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135300044</v>
       </c>
       <c r="B27" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135510816</v>
       </c>
       <c r="B28" t="n">
-        <v>90766</v>
+        <v>90793</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135293869</v>
       </c>
       <c r="B29" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135331647</v>
       </c>
       <c r="B30" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>135305591</v>
       </c>
       <c r="B31" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>135293775</v>
       </c>
       <c r="B32" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135331645</v>
       </c>
       <c r="B33" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135293801</v>
       </c>
       <c r="B34" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4656,7 +4656,7 @@
         <v>135293816</v>
       </c>
       <c r="B35" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>135293824</v>
       </c>
       <c r="B36" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135293849</v>
       </c>
       <c r="B37" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>135331638</v>
       </c>
       <c r="B38" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>135293784</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>135293785</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135293792</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5468,7 +5468,7 @@
         <v>135293794</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>135293800</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>135293803</v>
       </c>
       <c r="B44" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>135293808</v>
       </c>
       <c r="B45" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135293814</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>135293822</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>135293831</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>135293843</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6396,7 +6396,7 @@
         <v>135293866</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135293867</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>135293868</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135293870</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>135293885</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>135293888</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>135293892</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>135293894</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>135293895</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>135293896</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>135293898</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>135293899</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>135293901</v>
       </c>
       <c r="B62" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>135293903</v>
       </c>
       <c r="B63" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>135293908</v>
       </c>
       <c r="B64" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>135293918</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>135297982</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>135297987</v>
       </c>
       <c r="B67" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>135297995</v>
       </c>
       <c r="B68" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>135298003</v>
       </c>
       <c r="B69" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>135298005</v>
       </c>
       <c r="B70" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>135298008</v>
       </c>
       <c r="B71" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>135298016</v>
       </c>
       <c r="B72" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>135298018</v>
       </c>
       <c r="B73" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>135298022</v>
       </c>
       <c r="B74" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>135298624</v>
       </c>
       <c r="B75" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>135298625</v>
       </c>
       <c r="B76" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>135298634</v>
       </c>
       <c r="B77" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>135298640</v>
       </c>
       <c r="B78" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>135298641</v>
       </c>
       <c r="B79" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>135298643</v>
       </c>
       <c r="B80" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>135298650</v>
       </c>
       <c r="B81" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>135300029</v>
       </c>
       <c r="B82" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>135300030</v>
       </c>
       <c r="B83" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>135300034</v>
       </c>
       <c r="B84" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>135300045</v>
       </c>
       <c r="B85" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>135305574</v>
       </c>
       <c r="B86" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>135331589</v>
       </c>
       <c r="B87" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>135331597</v>
       </c>
       <c r="B88" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>135331606</v>
       </c>
       <c r="B89" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>135331611</v>
       </c>
       <c r="B90" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>135331612</v>
       </c>
       <c r="B91" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135331615</v>
       </c>
       <c r="B92" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>135331625</v>
       </c>
       <c r="B93" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>135331626</v>
       </c>
       <c r="B94" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>135331627</v>
       </c>
       <c r="B95" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>135331629</v>
       </c>
       <c r="B96" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>135331642</v>
       </c>
       <c r="B97" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>135293776</v>
       </c>
       <c r="B98" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>135293783</v>
       </c>
       <c r="B99" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>135293791</v>
       </c>
       <c r="B100" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12402,7 +12402,7 @@
         <v>135293795</v>
       </c>
       <c r="B101" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>135293810</v>
       </c>
       <c r="B102" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>135293820</v>
       </c>
       <c r="B103" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>135293846</v>
       </c>
       <c r="B104" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>135293851</v>
       </c>
       <c r="B105" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>135293854</v>
       </c>
       <c r="B106" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13098,7 +13098,7 @@
         <v>135293857</v>
       </c>
       <c r="B107" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>135293878</v>
       </c>
       <c r="B108" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135293881</v>
       </c>
       <c r="B109" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>135297981</v>
       </c>
       <c r="B110" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>135297992</v>
       </c>
       <c r="B111" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>135298001</v>
       </c>
       <c r="B112" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>135298012</v>
       </c>
       <c r="B113" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>135300025</v>
       </c>
       <c r="B114" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>135300027</v>
       </c>
       <c r="B115" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>135300032</v>
       </c>
       <c r="B116" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>135300040</v>
       </c>
       <c r="B117" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>135305585</v>
       </c>
       <c r="B118" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>135331603</v>
       </c>
       <c r="B119" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>135331637</v>
       </c>
       <c r="B120" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>135293889</v>
       </c>
       <c r="B121" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>135298009</v>
       </c>
       <c r="B122" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>135298019</v>
       </c>
       <c r="B123" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>135300046</v>
       </c>
       <c r="B124" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>135305578</v>
       </c>
       <c r="B125" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>135331610</v>
       </c>
       <c r="B126" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>135300042</v>
       </c>
       <c r="B127" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>135331621</v>
       </c>
       <c r="B128" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>135293774</v>
       </c>
       <c r="B129" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>135293780</v>
       </c>
       <c r="B130" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>135293787</v>
       </c>
       <c r="B131" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>135293806</v>
       </c>
       <c r="B132" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>135293811</v>
       </c>
       <c r="B133" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>135293812</v>
       </c>
       <c r="B134" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16511,7 +16511,7 @@
         <v>135293817</v>
       </c>
       <c r="B135" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>135293829</v>
       </c>
       <c r="B136" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>135293833</v>
       </c>
       <c r="B137" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -16859,7 +16859,7 @@
         <v>135293855</v>
       </c>
       <c r="B138" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>135293858</v>
       </c>
       <c r="B139" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>135293875</v>
       </c>
       <c r="B140" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>135293877</v>
       </c>
       <c r="B141" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>135297990</v>
       </c>
       <c r="B142" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>135298631</v>
       </c>
       <c r="B143" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>135300041</v>
       </c>
       <c r="B144" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>135305570</v>
       </c>
       <c r="B145" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>135331591</v>
       </c>
       <c r="B146" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135331592</v>
       </c>
       <c r="B147" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>135331595</v>
       </c>
       <c r="B148" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>135331598</v>
       </c>
       <c r="B149" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>135331599</v>
       </c>
       <c r="B150" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>135331608</v>
       </c>
       <c r="B151" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>135331622</v>
       </c>
       <c r="B152" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>135331632</v>
       </c>
       <c r="B153" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>135331633</v>
       </c>
       <c r="B154" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>135512789</v>
       </c>
       <c r="B155" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>135298623</v>
       </c>
       <c r="B156" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>135511061</v>
       </c>
       <c r="B157" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>135293805</v>
       </c>
       <c r="B158" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>135293871</v>
       </c>
       <c r="B159" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>135293886</v>
       </c>
       <c r="B160" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>135293882</v>
       </c>
       <c r="B161" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>135297978</v>
       </c>
       <c r="B162" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>135297993</v>
       </c>
       <c r="B163" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135298648</v>
       </c>
       <c r="B164" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>135293848</v>
       </c>
       <c r="B165" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>135293872</v>
       </c>
       <c r="B166" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>135293786</v>
       </c>
       <c r="B167" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>135293790</v>
       </c>
       <c r="B168" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>135293796</v>
       </c>
       <c r="B169" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>135293818</v>
       </c>
       <c r="B170" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>135293823</v>
       </c>
       <c r="B171" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -20943,7 +20943,7 @@
         <v>135293842</v>
       </c>
       <c r="B172" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>135297991</v>
       </c>
       <c r="B173" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>135297999</v>
       </c>
       <c r="B174" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>135298000</v>
       </c>
       <c r="B175" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>135300026</v>
       </c>
       <c r="B176" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>135300028</v>
       </c>
       <c r="B177" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>135300033</v>
       </c>
       <c r="B178" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>135305583</v>
       </c>
       <c r="B179" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>135331601</v>
       </c>
       <c r="B180" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>135331636</v>
       </c>
       <c r="B181" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>135298647</v>
       </c>
       <c r="B250" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>135298652</v>
       </c>
       <c r="B251" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>135298658</v>
       </c>
       <c r="B252" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>135298659</v>
       </c>
       <c r="B253" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>135300049</v>
       </c>
       <c r="B254" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>135300050</v>
       </c>
       <c r="B255" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>135298626</v>
       </c>
       <c r="B256" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>135298642</v>
       </c>
       <c r="B257" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>135298645</v>
       </c>
       <c r="B258" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>135298655</v>
       </c>
       <c r="B259" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>135305575</v>
       </c>
       <c r="B260" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>135305587</v>
       </c>
       <c r="B261" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>135300024</v>
       </c>
       <c r="B262" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>135305577</v>
       </c>
       <c r="B263" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>135513209</v>
       </c>
       <c r="B264" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>135300036</v>
       </c>
       <c r="B265" t="n">
-        <v>103958</v>
+        <v>103985</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>135300047</v>
       </c>
       <c r="B266" t="n">
-        <v>103958</v>
+        <v>103985</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>135297980</v>
       </c>
       <c r="B267" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>135297985</v>
       </c>
       <c r="B268" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>135297998</v>
       </c>
       <c r="B269" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>135298006</v>
       </c>
       <c r="B270" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>135293821</v>
       </c>
       <c r="B271" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
@@ -33442,7 +33442,7 @@
         <v>135293852</v>
       </c>
       <c r="B272" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>135293874</v>
       </c>
       <c r="B273" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>135293880</v>
       </c>
       <c r="B274" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>135293917</v>
       </c>
       <c r="B275" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>135297989</v>
       </c>
       <c r="B276" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>135298004</v>
       </c>
       <c r="B277" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>135299553</v>
       </c>
       <c r="B278" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>135299554</v>
       </c>
       <c r="B279" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>135300038</v>
       </c>
       <c r="B280" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>135300043</v>
       </c>
       <c r="B281" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>135305584</v>
       </c>
       <c r="B282" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>135331620</v>
       </c>
       <c r="B283" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>135331623</v>
       </c>
       <c r="B284" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>135331630</v>
       </c>
       <c r="B285" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>135293793</v>
       </c>
       <c r="B286" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -35247,7 +35247,7 @@
         <v>135293819</v>
       </c>
       <c r="B287" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>135293825</v>
       </c>
       <c r="B288" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>135293828</v>
       </c>
       <c r="B289" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>135293832</v>
       </c>
       <c r="B290" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
@@ -35711,7 +35711,7 @@
         <v>135293845</v>
       </c>
       <c r="B291" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Lina Hällström, Torun Ingrid Maria Jacobsson, Johan Råghall, Klas Magnusson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
@@ -35827,7 +35827,7 @@
         <v>135293847</v>
       </c>
       <c r="B292" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>135293879</v>
       </c>
       <c r="B293" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>135300039</v>
       </c>
       <c r="B294" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>135331588</v>
       </c>
       <c r="B295" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>135331593</v>
       </c>
       <c r="B296" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>135331594</v>
       </c>
       <c r="B297" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>135331617</v>
       </c>
       <c r="B298" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>135331628</v>
       </c>
       <c r="B299" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>135293777</v>
       </c>
       <c r="B300" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>135293856</v>
       </c>
       <c r="B301" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson, Mattias Dalkvist, Isak Falk Eliasson</t>
+          <t>Cajsa Björkén, Isak Falk Eliasson, Mattias Dalkvist, Klas Magnusson, Johan Råghall, Torun Ingrid Maria Jacobsson, Lina Hällström, Marie Persson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -37002,7 +37002,7 @@
         <v>135298629</v>
       </c>
       <c r="B302" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>135298633</v>
       </c>
       <c r="B303" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>135298639</v>
       </c>
       <c r="B304" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>135298657</v>
       </c>
       <c r="B305" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>135331590</v>
       </c>
       <c r="B306" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>135331596</v>
       </c>
       <c r="B307" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>135331605</v>
       </c>
       <c r="B308" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>135331607</v>
       </c>
       <c r="B309" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>135331609</v>
       </c>
       <c r="B310" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>135331618</v>
       </c>
       <c r="B311" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>135331640</v>
       </c>
       <c r="B312" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>135331644</v>
       </c>
       <c r="B313" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>135331646</v>
       </c>
       <c r="B314" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>135293815</v>
       </c>
       <c r="B315" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>135293827</v>
       </c>
       <c r="B316" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>135305595</v>
       </c>
       <c r="B317" t="n">
-        <v>95884</v>
+        <v>95911</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135305579</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>135331631</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>135293798</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135331635</v>
       </c>
       <c r="B5" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2573,7 +2573,7 @@
         <v>135305590</v>
       </c>
       <c r="B18" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3061,7 +3061,7 @@
         <v>135305592</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>135293779</v>
       </c>
       <c r="B24" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135293781</v>
       </c>
       <c r="B25" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>135298017</v>
       </c>
       <c r="B26" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>135300044</v>
       </c>
       <c r="B27" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135510816</v>
       </c>
       <c r="B28" t="n">
-        <v>90796</v>
+        <v>90798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135293869</v>
       </c>
       <c r="B29" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135331647</v>
       </c>
       <c r="B30" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>135305591</v>
       </c>
       <c r="B31" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>135293775</v>
       </c>
       <c r="B32" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>135331645</v>
       </c>
       <c r="B33" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>135293801</v>
       </c>
       <c r="B34" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135293816</v>
       </c>
       <c r="B35" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>135293824</v>
       </c>
       <c r="B36" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135293849</v>
       </c>
       <c r="B37" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>135331638</v>
       </c>
       <c r="B38" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -30773,7 +30773,7 @@
         <v>135298647</v>
       </c>
       <c r="B250" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -30894,7 +30894,7 @@
         <v>135298652</v>
       </c>
       <c r="B251" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>135298658</v>
       </c>
       <c r="B252" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>135298659</v>
       </c>
       <c r="B253" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>135300049</v>
       </c>
       <c r="B254" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>135300050</v>
       </c>
       <c r="B255" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>135298626</v>
       </c>
       <c r="B256" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>135298642</v>
       </c>
       <c r="B257" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
@@ -31759,7 +31759,7 @@
         <v>135298645</v>
       </c>
       <c r="B258" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -31880,7 +31880,7 @@
         <v>135298655</v>
       </c>
       <c r="B259" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>135305575</v>
       </c>
       <c r="B260" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>135305587</v>
       </c>
       <c r="B261" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>135300024</v>
       </c>
       <c r="B262" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>135305577</v>
       </c>
       <c r="B263" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>135513209</v>
       </c>
       <c r="B264" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>135300036</v>
       </c>
       <c r="B265" t="n">
-        <v>103990</v>
+        <v>103992</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>135300047</v>
       </c>
       <c r="B266" t="n">
-        <v>103990</v>
+        <v>103992</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Lina Hällström, Klas Magnusson, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
+          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Klas Magnusson, Lina Hällström, Johan Råghall, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -38763,7 +38763,7 @@
         <v>135305595</v>
       </c>
       <c r="B317" t="n">
-        <v>95916</v>
+        <v>95918</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -31740,7 +31740,7 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
@@ -31861,7 +31861,7 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Lina Hällström, Klas Magnusson, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Klas Magnusson, Lina Hällström, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -37335,7 +37335,7 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Marie Persson, Klas Magnusson, Lina Hällström, Johan Råghall, Cajsa Björkén</t>
+          <t>Isak Falk Eliasson, Cajsa Björkén, Johan Råghall, Lina Hällström, Klas Magnusson, Marie Persson, Mattias Dalkvist, Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135305579</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135305590</v>
       </c>
       <c r="B18" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>135305592</v>
       </c>
       <c r="B22" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135510816</v>
       </c>
       <c r="B28" t="n">
-        <v>90798</v>
+        <v>90800</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>135305591</v>
       </c>
       <c r="B31" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>135305574</v>
       </c>
       <c r="B86" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>135305585</v>
       </c>
       <c r="B118" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>135305578</v>
       </c>
       <c r="B125" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>135305570</v>
       </c>
       <c r="B145" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>135512789</v>
       </c>
       <c r="B155" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>135298623</v>
       </c>
       <c r="B156" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>135511061</v>
       </c>
       <c r="B157" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>135305583</v>
       </c>
       <c r="B179" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>135293897</v>
       </c>
       <c r="B187" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>135293905</v>
       </c>
       <c r="B191" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>135511047</v>
       </c>
       <c r="B227" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>135512979</v>
       </c>
       <c r="B228" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>135513031</v>
       </c>
       <c r="B229" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>135513062</v>
       </c>
       <c r="B230" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>135305567</v>
       </c>
       <c r="B233" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>135305572</v>
       </c>
       <c r="B234" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>135305582</v>
       </c>
       <c r="B235" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>135305571</v>
       </c>
       <c r="B239" t="n">
-        <v>5497</v>
+        <v>5498</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>135305581</v>
       </c>
       <c r="B244" t="n">
-        <v>58143</v>
+        <v>58145</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>135307481</v>
       </c>
       <c r="B247" t="n">
-        <v>6286</v>
+        <v>6288</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>135305600</v>
       </c>
       <c r="B248" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>135305596</v>
       </c>
       <c r="B249" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>135305575</v>
       </c>
       <c r="B260" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>135305587</v>
       </c>
       <c r="B261" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>135305577</v>
       </c>
       <c r="B263" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>135513209</v>
       </c>
       <c r="B264" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>135305584</v>
       </c>
       <c r="B282" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>135305595</v>
       </c>
       <c r="B317" t="n">
-        <v>95918</v>
+        <v>95935</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>

--- a/artfynd/A 30606-2025 artfynd.xlsx
+++ b/artfynd/A 30606-2025 artfynd.xlsx
@@ -3802,7 +3802,7 @@
         <v>135510816</v>
       </c>
       <c r="B28" t="n">
-        <v>90800</v>
+        <v>90801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>135512789</v>
       </c>
       <c r="B155" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>135298623</v>
       </c>
       <c r="B156" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>135511061</v>
       </c>
       <c r="B157" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>135513209</v>
       </c>
       <c r="B264" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
